--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_8_R1.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_8_R1.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0413</v>
+        <v>7.5878</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6223</v>
+        <v>5.1688</v>
       </c>
       <c r="F2" t="n">
         <v>2.4191</v>
@@ -610,10 +610,10 @@
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6553</v>
+        <v>-1.1088</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3364</v>
+        <v>-0.7899</v>
       </c>
       <c r="U2" t="n">
         <v>-0.3189</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2072</v>
+        <v>3.5735</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4203</v>
+        <v>1.5514</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7869</v>
+        <v>2.0221</v>
       </c>
       <c r="G3" t="n">
         <v>2.4518</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8096</v>
+        <v>0.1759</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9085</v>
+        <v>0.0395</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0988</v>
+        <v>0.1364</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6778999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.102</v>
+        <v>3.0671</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7816</v>
+        <v>1.3098</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3204</v>
+        <v>1.7573</v>
       </c>
       <c r="G4" t="n">
         <v>3.1427</v>
@@ -766,13 +766,13 @@
         <v>3.0154</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3913</v>
+        <v>-1.4262</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.55</v>
+        <v>-1.0218</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8413</v>
+        <v>-0.4044</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5051</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. MELLI</t>
+          <t>B. COLSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7048</v>
+        <v>2.894</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5758</v>
+        <v>0.6579</v>
       </c>
       <c r="F5" t="n">
-        <v>2.129</v>
+        <v>2.2361</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0082</v>
+        <v>0.5908</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3218</v>
+        <v>2.8594</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6864</v>
+        <v>-2.2686</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1362</v>
+        <v>0.2081</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.1862</v>
+        <v>1.6336</v>
       </c>
       <c r="L5" t="n">
-        <v>3.3224</v>
+        <v>-1.4255</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.128</v>
+        <v>0.3827</v>
       </c>
       <c r="N5" t="n">
-        <v>1.508</v>
+        <v>1.2258</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.636</v>
+        <v>-0.8431</v>
       </c>
       <c r="P5" t="n">
         <v>1.8556</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0154</v>
+        <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6229</v>
+        <v>-0.0885</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4007</v>
+        <v>-0.0863</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2223</v>
+        <v>-0.0022</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5361</v>
+        <v>0.5361</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. COLSON</t>
+          <t>N. MELLI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6073</v>
+        <v>2.1403</v>
       </c>
       <c r="E6" t="n">
-        <v>0.304</v>
+        <v>0.4146</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3033</v>
+        <v>1.7257</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5908</v>
+        <v>2.0082</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8594</v>
+        <v>0.3218</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.2686</v>
+        <v>1.6864</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2081</v>
+        <v>2.1362</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6336</v>
+        <v>-1.1862</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4255</v>
+        <v>3.3224</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3827</v>
+        <v>-0.128</v>
       </c>
       <c r="N6" t="n">
-        <v>1.2258</v>
+        <v>1.508</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8431</v>
+        <v>-1.636</v>
       </c>
       <c r="P6" t="n">
         <v>1.8556</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8556</v>
+        <v>3.0154</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3752</v>
+        <v>-1.1874</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4402</v>
+        <v>-0.5619</v>
       </c>
       <c r="U6" t="n">
-        <v>0.065</v>
+        <v>-0.6256</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5361</v>
+        <v>-0.5361</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8943</v>
+        <v>1.827</v>
       </c>
       <c r="E7" t="n">
         <v>1.0939</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8004</v>
+        <v>0.7332</v>
       </c>
       <c r="G7" t="n">
         <v>1.1868</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1713</v>
+        <v>0.1041</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1713</v>
+        <v>0.1041</v>
       </c>
       <c r="V7" t="n">
         <v>0.5361</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2978</v>
+        <v>0.2051</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.847</v>
+        <v>-2.5365</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1449</v>
+        <v>2.7416</v>
       </c>
       <c r="G8" t="n">
         <v>1.0037</v>
@@ -1078,13 +1078,13 @@
         <v>2.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.028</v>
+        <v>-1.1206</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1949</v>
+        <v>-0.8843</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1669</v>
+        <v>-0.2363</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1418</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.17</v>
+        <v>0.0191</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3914</v>
+        <v>-1.2735</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5614</v>
+        <v>1.2925</v>
       </c>
       <c r="G9" t="n">
         <v>0.8526</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4507</v>
+        <v>-0.6016</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4481</v>
+        <v>-0.3301</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0026</v>
+        <v>-0.2715</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. BITIM</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4445</v>
+        <v>-0.0849</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8832</v>
+        <v>-0.9548</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4387</v>
+        <v>0.8698</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8496</v>
+        <v>1.88</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6399</v>
+        <v>1.9101</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4894</v>
+        <v>-0.03</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3604</v>
+        <v>1.0579</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4502</v>
+        <v>0.8739</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.9102</v>
+        <v>0.184</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4891</v>
+        <v>0.8222</v>
       </c>
       <c r="N10" t="n">
-        <v>1.0901</v>
+        <v>1.0362</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5792</v>
+        <v>-0.214</v>
       </c>
       <c r="P10" t="n">
         <v>0.6959</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8681</v>
+        <v>-1.4468</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5228</v>
+        <v>-0.8529</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3453</v>
+        <v>-0.5939</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5773</v>
+        <v>-1.214</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.5773</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>O. BITIM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4717</v>
+        <v>-0.2429</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0727</v>
+        <v>-1.8832</v>
       </c>
       <c r="F11" t="n">
-        <v>0.601</v>
+        <v>1.6403</v>
       </c>
       <c r="G11" t="n">
-        <v>1.88</v>
+        <v>-1.8496</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9101</v>
+        <v>0.6399</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.03</v>
+        <v>-2.4894</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0579</v>
+        <v>-1.3604</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8739</v>
+        <v>-0.4502</v>
       </c>
       <c r="L11" t="n">
-        <v>0.184</v>
+        <v>-0.9102</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8222</v>
+        <v>-0.4891</v>
       </c>
       <c r="N11" t="n">
-        <v>1.0362</v>
+        <v>1.0901</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.214</v>
+        <v>-1.5792</v>
       </c>
       <c r="P11" t="n">
         <v>0.6959</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8336</v>
+        <v>-0.6664</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9709</v>
+        <v>-0.5228</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8628</v>
+        <v>-0.1436</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.214</v>
+        <v>1.5773</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.214</v>
+        <v>1.5773</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3095</v>
+        <v>-2.158</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7921</v>
+        <v>-1.6741</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5174</v>
+        <v>-0.4838</v>
       </c>
       <c r="G12" t="n">
         <v>0.31</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2278</v>
+        <v>-1.0763</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6721</v>
+        <v>-0.5542</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5557</v>
+        <v>-0.5221</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.5405</v>
+        <v>-2.1963</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2912</v>
+        <v>-0.9806</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2493</v>
+        <v>-1.2157</v>
       </c>
       <c r="G13" t="n">
         <v>1.3342</v>
@@ -1468,13 +1468,13 @@
         <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0038</v>
+        <v>-0.6596</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8962</v>
+        <v>-0.5856</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1076</v>
+        <v>-0.074</v>
       </c>
       <c r="V13" t="n">
         <v>1.0722</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>16.2585</v>
+        <v>16.63179999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5202999999999993</v>
+        <v>0.8937000000000005</v>
       </c>
       <c r="F14" t="n">
-        <v>15.7384</v>
+        <v>15.7382</v>
       </c>
       <c r="G14" t="n">
         <v>22.0897</v>
@@ -1546,13 +1546,13 @@
         <v>20.8757</v>
       </c>
       <c r="S14" t="n">
-        <v>-9.4758</v>
+        <v>-9.1022</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.523800000000001</v>
+        <v>-6.150300000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.9521</v>
+        <v>-2.952</v>
       </c>
       <c r="V14" t="n">
         <v>1.3247</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.471</v>
+        <v>4.4767</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2067</v>
+        <v>2.0887</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2643</v>
+        <v>2.388</v>
       </c>
       <c r="G15" t="n">
         <v>1.5552</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>0.988</v>
+        <v>0.9937</v>
       </c>
       <c r="T15" t="n">
-        <v>0.362</v>
+        <v>0.244</v>
       </c>
       <c r="U15" t="n">
-        <v>0.626</v>
+        <v>0.7497</v>
       </c>
       <c r="V15" t="n">
         <v>0.5361</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>A. M'BAYE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8137</v>
+        <v>2.1838</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8327</v>
+        <v>0.4199</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9809</v>
+        <v>1.7639</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1251</v>
+        <v>-1.0197</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4369</v>
+        <v>-1.6856</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5620000000000001</v>
+        <v>0.6659</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1325</v>
+        <v>-0.3945</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3228</v>
+        <v>-1.4852</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8097</v>
+        <v>1.0907</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2576</v>
+        <v>-0.6252</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1141</v>
+        <v>-0.2004</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3717</v>
+        <v>-0.4248</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4639</v>
+        <v>2.0876</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>3.6888</v>
+        <v>0.9741</v>
       </c>
       <c r="T16" t="n">
-        <v>1.86</v>
+        <v>0.6726</v>
       </c>
       <c r="U16" t="n">
-        <v>1.8288</v>
+        <v>0.3016</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.214</v>
+        <v>0.1418</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. M'BAYE</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5782</v>
+        <v>1.2036</v>
       </c>
       <c r="E17" t="n">
-        <v>0.184</v>
+        <v>0.7712</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3942</v>
+        <v>0.4325</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0197</v>
+        <v>-0.1251</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.6856</v>
+        <v>0.4369</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6659</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3945</v>
+        <v>1.1325</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.4852</v>
+        <v>0.3228</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0907</v>
+        <v>0.8097</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6252</v>
+        <v>-1.2576</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2004</v>
+        <v>0.1141</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4248</v>
+        <v>-1.3717</v>
       </c>
       <c r="P17" t="n">
-        <v>2.0876</v>
+        <v>0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3686</v>
+        <v>2.0788</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4367</v>
+        <v>0.7984</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.06809999999999999</v>
+        <v>1.2803</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1418</v>
+        <v>-1.214</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. HOMMES</t>
+          <t>N. HIFI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4633</v>
+        <v>0.2158</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5603</v>
+        <v>1.5403</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.097</v>
+        <v>-1.3245</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0194</v>
+        <v>-0.482</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7886</v>
+        <v>-6.508</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2309</v>
+        <v>6.026</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1182</v>
+        <v>2.5918</v>
       </c>
       <c r="K18" t="n">
-        <v>0.08400000000000001</v>
+        <v>-4.9632</v>
       </c>
       <c r="L18" t="n">
-        <v>2.0342</v>
+        <v>7.5549</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.1377</v>
+        <v>-3.0738</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8726</v>
+        <v>-1.5448</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.2651</v>
+        <v>-1.529</v>
       </c>
       <c r="P18" t="n">
-        <v>0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3926</v>
+        <v>0.8729</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6018</v>
+        <v>0.2833</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7907</v>
+        <v>0.5895</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1418</v>
+        <v>2.1444</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>D. HOMMES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2052</v>
+        <v>0.1323</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2864</v>
+        <v>1.2064</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4916</v>
+        <v>-1.0742</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0964</v>
+        <v>-1.0194</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1465</v>
+        <v>-0.7886</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0501</v>
+        <v>-0.2309</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9507</v>
+        <v>2.1182</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1104</v>
+        <v>2.0342</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-3.1377</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6938</v>
+        <v>-0.8726</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1605</v>
+        <v>-2.2651</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3763</v>
+        <v>1.0616</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7275</v>
+        <v>0.248</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6489</v>
+        <v>0.8136</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.214</v>
+        <v>-0.1418</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.214</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.545</v>
+        <v>-0.259</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4682</v>
+        <v>-1.3503</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9233</v>
+        <v>1.0913</v>
       </c>
       <c r="G20" t="n">
         <v>0.806</v>
@@ -2014,13 +2014,13 @@
         <v>2.3195</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4582</v>
+        <v>0.7442</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0712</v>
+        <v>0.1891</v>
       </c>
       <c r="U20" t="n">
-        <v>0.387</v>
+        <v>0.5551</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5773</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. HIFI</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5807</v>
+        <v>-0.7943</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3044</v>
+        <v>-0.0674</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.885</v>
+        <v>-0.7269</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.482</v>
+        <v>0.0964</v>
       </c>
       <c r="H21" t="n">
-        <v>-6.508</v>
+        <v>0.1465</v>
       </c>
       <c r="I21" t="n">
-        <v>6.026</v>
+        <v>-0.0501</v>
       </c>
       <c r="J21" t="n">
-        <v>2.5918</v>
+        <v>0.9507</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.9632</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>7.5549</v>
+        <v>0.1104</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.0738</v>
+        <v>-0.8542999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5448</v>
+        <v>-0.6938</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.529</v>
+        <v>-0.1605</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.3195</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4793</v>
+        <v>-1.3917</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0764</v>
+        <v>0.7872</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0474</v>
+        <v>0.3736</v>
       </c>
       <c r="U21" t="n">
-        <v>0.029</v>
+        <v>0.4136</v>
       </c>
       <c r="V21" t="n">
-        <v>2.1444</v>
+        <v>-1.214</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7387</v>
+        <v>-3.2276</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7662</v>
+        <v>-3.4124</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0275</v>
+        <v>0.1848</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2132</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7038</v>
+        <v>1.2149</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1142</v>
+        <v>0.4681</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5895</v>
+        <v>0.7468</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1418</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. WILLIS</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2168</v>
+        <v>-3.6013</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3949</v>
+        <v>-4.9436</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8219</v>
+        <v>1.3423</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.0634</v>
+        <v>-4.7763</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.1992</v>
+        <v>-0.9351</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.8641</v>
+        <v>-3.8413</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.8858</v>
+        <v>-4.4868</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4972</v>
+        <v>-0.7023</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3887</v>
+        <v>-3.7845</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.1775</v>
+        <v>-0.2895</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7021</v>
+        <v>-0.2327</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4755</v>
+        <v>-0.0568</v>
       </c>
       <c r="P23" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6146</v>
+        <v>0.1751</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0272</v>
+        <v>-0.1373</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6418</v>
+        <v>0.3123</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6778999999999999</v>
+        <v>1.0722</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>D. WILLIS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4256</v>
+        <v>-4.1325</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.2975</v>
+        <v>-2.277</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8718</v>
+        <v>-1.8555</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.7763</v>
+        <v>-5.0634</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9351</v>
+        <v>-2.1992</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.8413</v>
+        <v>-2.8641</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.4868</v>
+        <v>-1.8858</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7023</v>
+        <v>-0.4972</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.7845</v>
+        <v>-1.3887</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2895</v>
+        <v>-3.1775</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2327</v>
+        <v>-1.7021</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0568</v>
+        <v>-1.4755</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6493</v>
+        <v>0.6989</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4911</v>
+        <v>0.0907</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1581</v>
+        <v>0.6082</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0722</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5361</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.8925</v>
+        <v>-5.1113</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.995</v>
+        <v>-3.1129</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8975</v>
+        <v>-1.9984</v>
       </c>
       <c r="G25" t="n">
         <v>-1.9031</v>
@@ -2404,13 +2404,13 @@
         <v>0.9278</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2631</v>
+        <v>0.0444</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0395</v>
+        <v>-0.0784</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2236</v>
+        <v>0.1228</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8608</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.98</v>
+        <v>-6.5583</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.1909</v>
+        <v>-6.6011</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2109</v>
+        <v>0.0428</v>
       </c>
       <c r="G26" t="n">
         <v>-7.9453</v>
@@ -2482,13 +2482,13 @@
         <v>1.8556</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1946</v>
+        <v>0.6163</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.7899</v>
+        <v>-0.2001</v>
       </c>
       <c r="U26" t="n">
-        <v>0.9845</v>
+        <v>0.8164</v>
       </c>
       <c r="V26" t="n">
         <v>1.4665</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-16.2583</v>
+        <v>-15.4721</v>
       </c>
       <c r="E27" t="n">
         <v>-15.7382</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.5200999999999999</v>
+        <v>0.2660999999999994</v>
       </c>
       <c r="G27" t="n">
         <v>-22.0899</v>
@@ -2560,19 +2560,19 @@
         <v>18.5562</v>
       </c>
       <c r="S27" t="n">
-        <v>9.4757</v>
+        <v>10.2621</v>
       </c>
       <c r="T27" t="n">
-        <v>2.9521</v>
+        <v>2.952</v>
       </c>
       <c r="U27" t="n">
-        <v>6.5236</v>
+        <v>7.309900000000001</v>
       </c>
       <c r="V27" t="n">
-        <v>-1.3248</v>
+        <v>-1.324799999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>4.350899999999999</v>
+        <v>4.350900000000001</v>
       </c>
       <c r="X27" t="n">
         <v>-5.6757</v>
